--- a/资源库/模型选用表.xlsx
+++ b/资源库/模型选用表.xlsx
@@ -859,18 +859,6 @@
     <t>品牌标识/墙面LOGO_影石Insta360始于敢想_1266mm_B__asset-33868330</t>
   </si>
   <si>
-    <t>影石全景相机墙面LOGO</t>
-  </si>
-  <si>
-    <t>asset-33868332</t>
-  </si>
-  <si>
-    <t>4673 × 50 × 405</t>
-  </si>
-  <si>
-    <t>品牌标识/墙面LOGO_影石Insta360全景相机_4673mm__asset-33868332</t>
-  </si>
-  <si>
     <t>Insta360墙面LOGO</t>
   </si>
   <si>
@@ -920,6 +908,18 @@
   </si>
   <si>
     <t>品牌标识/墙面LOGO_影石Insta360始于敢想_1267mm_A__asset-6952129</t>
+  </si>
+  <si>
+    <t>影石徕卡联名墙面LOGO</t>
+  </si>
+  <si>
+    <t>asset-90000001</t>
+  </si>
+  <si>
+    <t>2400 × 30 × 509</t>
+  </si>
+  <si>
+    <t>品牌标识/墙面LOGO_影石Insta360徕卡联名_2400mm__asset-90000001</t>
   </si>
   <si>
     <t>影石双面侧招</t>
@@ -4936,7 +4936,7 @@
       <xdr:row>63</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="657225"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="96" name="Picture 96">
@@ -4975,7 +4975,7 @@
       <xdr:row>64</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="438150"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="97" name="Picture 97">
@@ -5014,7 +5014,7 @@
       <xdr:row>65</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="438150"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="98" name="Picture 98">
@@ -5053,7 +5053,7 @@
       <xdr:row>66</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="314325"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="99" name="Picture 99">
@@ -5092,7 +5092,7 @@
       <xdr:row>67</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="438150"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="100" name="Picture 100">
@@ -5131,7 +5131,7 @@
       <xdr:row>68</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="657225"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="101" name="Picture 101">
@@ -5170,7 +5170,7 @@
       <xdr:row>69</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="800100"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="102" name="Picture 102">
@@ -5209,7 +5209,7 @@
       <xdr:row>70</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="323850"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="103" name="Picture 103">
@@ -5248,7 +5248,7 @@
       <xdr:row>71</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="438150"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="104" name="Picture 104">
@@ -5287,7 +5287,7 @@
       <xdr:row>72</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="523875"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="105" name="Picture 105">
@@ -5326,7 +5326,7 @@
       <xdr:row>73</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="657225"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="106" name="Picture 106">
@@ -5365,7 +5365,7 @@
       <xdr:row>74</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="561975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="107" name="Picture 107">
@@ -5443,7 +5443,7 @@
       <xdr:row>76</xdr:row>
       <xdr:rowOff>67200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1333500"/>
+    <xdr:ext cx="1905000" cy="523875"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="109" name="Picture 109">
@@ -10389,7 +10389,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>15</v>
@@ -10413,7 +10413,7 @@
         <v>15</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>255</v>
@@ -10422,10 +10422,10 @@
         <v>15</v>
       </c>
       <c r="M72" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="N72" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="73" ht="112" customHeight="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10433,7 +10433,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>15</v>
@@ -10457,7 +10457,7 @@
         <v>15</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>255</v>
@@ -10466,10 +10466,10 @@
         <v>15</v>
       </c>
       <c r="M73" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="N73" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="74" ht="112" customHeight="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10477,7 +10477,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -10501,7 +10501,7 @@
         <v>15</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>255</v>
@@ -10510,10 +10510,10 @@
         <v>15</v>
       </c>
       <c r="M74" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="N74" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="75" ht="112" customHeight="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10521,7 +10521,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>15</v>

--- a/资源库/模型选用表.xlsx
+++ b/资源库/模型选用表.xlsx
@@ -916,10 +916,10 @@
     <t>asset-90000001</t>
   </si>
   <si>
-    <t>2400 × 30 × 509</t>
-  </si>
-  <si>
-    <t>品牌标识/墙面LOGO_影石Insta360徕卡联名_2400mm__asset-90000001</t>
+    <t>880 × 15 × 187</t>
+  </si>
+  <si>
+    <t>品牌标识/墙面LOGO_影石Insta360徕卡联名_880mm__asset-90000001</t>
   </si>
   <si>
     <t>影石双面侧招</t>
@@ -940,7 +940,7 @@
     <t>asset-3147733</t>
   </si>
   <si>
-    <t>500 × 0 × 100</t>
+    <t>500 × 5 × 100</t>
   </si>
   <si>
     <t>品牌标识/LOGO画面_Insta360_500x100_平面__asset-3147733</t>
